--- a/artfynd/A 25758-2025 artfynd.xlsx
+++ b/artfynd/A 25758-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129500571</v>
       </c>
       <c r="B2" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129500567</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129500550</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129500572</v>
       </c>
       <c r="B5" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>129506764</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25758-2025 artfynd.xlsx
+++ b/artfynd/A 25758-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129500571</v>
       </c>
       <c r="B2" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129500567</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129500550</v>
       </c>
       <c r="B4" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129500572</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>129506764</v>
       </c>
       <c r="B6" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25758-2025 artfynd.xlsx
+++ b/artfynd/A 25758-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129500571</v>
       </c>
       <c r="B2" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129500567</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129500572</v>
       </c>
       <c r="B5" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25758-2025 artfynd.xlsx
+++ b/artfynd/A 25758-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129500571</v>
       </c>
       <c r="B2" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129500572</v>
       </c>
       <c r="B5" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25758-2025 artfynd.xlsx
+++ b/artfynd/A 25758-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129500571</v>
       </c>
       <c r="B2" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129500572</v>
       </c>
       <c r="B5" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25758-2025 artfynd.xlsx
+++ b/artfynd/A 25758-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129500571</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129500572</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129500547</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129500567</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129500568</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129500569</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129500570</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129500550</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129500551</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129506764</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1802,6 +1857,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129500556</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1909,8 +1969,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129500559</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>